--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Recoletas Salud San Pablo Burgos.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Recoletas Salud San Pablo Burgos.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>25.6624</v>
+        <v>40.6322</v>
       </c>
       <c r="E2" t="n">
-        <v>19.9334</v>
+        <v>34.2506</v>
       </c>
       <c r="F2" t="n">
-        <v>5.728800000000001</v>
+        <v>6.3813</v>
       </c>
       <c r="G2" t="n">
-        <v>-5.071299999999999</v>
+        <v>-4.8754</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6997</v>
+        <v>2.439499999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.7709</v>
+        <v>-7.3146</v>
       </c>
       <c r="J2" t="n">
-        <v>22.9846</v>
+        <v>33.223</v>
       </c>
       <c r="K2" t="n">
-        <v>15.9001</v>
+        <v>21.2854</v>
       </c>
       <c r="L2" t="n">
-        <v>7.084899999999999</v>
+        <v>11.9375</v>
       </c>
       <c r="M2" t="n">
-        <v>-28.0559</v>
+        <v>-38.0985</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.2003</v>
+        <v>-18.8461</v>
       </c>
       <c r="O2" t="n">
-        <v>-14.8556</v>
+        <v>-19.2522</v>
       </c>
       <c r="P2" t="n">
-        <v>5.6707</v>
+        <v>8.194699999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-39.242</v>
+        <v>-49.8513</v>
       </c>
       <c r="R2" t="n">
-        <v>44.9131</v>
+        <v>58.0458</v>
       </c>
       <c r="S2" t="n">
-        <v>25.2939</v>
+        <v>38.0982</v>
       </c>
       <c r="T2" t="n">
-        <v>18.9</v>
+        <v>30.3486</v>
       </c>
       <c r="U2" t="n">
-        <v>6.3938</v>
+        <v>7.7495</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2311000000000003</v>
+        <v>-0.7853000000000003</v>
       </c>
       <c r="W2" t="n">
-        <v>17.2908</v>
+        <v>20.5305</v>
       </c>
       <c r="X2" t="n">
-        <v>-17.522</v>
+        <v>-21.3155</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>21.5426</v>
+        <v>19.6926</v>
       </c>
       <c r="E3" t="n">
-        <v>19.6262</v>
+        <v>17.2436</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9162</v>
+        <v>2.4491</v>
       </c>
       <c r="G3" t="n">
-        <v>-7.190199999999999</v>
+        <v>-11.939</v>
       </c>
       <c r="H3" t="n">
-        <v>14.2305</v>
+        <v>5.888</v>
       </c>
       <c r="I3" t="n">
-        <v>-21.4206</v>
+        <v>-17.8267</v>
       </c>
       <c r="J3" t="n">
-        <v>37.1244</v>
+        <v>38.4138</v>
       </c>
       <c r="K3" t="n">
-        <v>37.7756</v>
+        <v>34.8839</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6514000000000006</v>
+        <v>3.5297</v>
       </c>
       <c r="M3" t="n">
-        <v>-44.3146</v>
+        <v>-50.3523</v>
       </c>
       <c r="N3" t="n">
-        <v>-23.5449</v>
+        <v>-28.9963</v>
       </c>
       <c r="O3" t="n">
-        <v>-20.7695</v>
+        <v>-21.3564</v>
       </c>
       <c r="P3" t="n">
-        <v>15.8784</v>
+        <v>16.8447</v>
       </c>
       <c r="Q3" t="n">
-        <v>-49.9034</v>
+        <v>-59.1845</v>
       </c>
       <c r="R3" t="n">
-        <v>65.7817</v>
+        <v>76.0287</v>
       </c>
       <c r="S3" t="n">
-        <v>-12.888</v>
+        <v>-18.701</v>
       </c>
       <c r="T3" t="n">
-        <v>-7.2854</v>
+        <v>-10.3691</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.6026</v>
+        <v>-8.331899999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>25.7426</v>
+        <v>33.4877</v>
       </c>
       <c r="W3" t="n">
-        <v>39.6906</v>
+        <v>48.3832</v>
       </c>
       <c r="X3" t="n">
-        <v>-13.9482</v>
+        <v>-14.8955</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. DIEZ</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>11.7782</v>
+        <v>7.3985</v>
       </c>
       <c r="E4" t="n">
-        <v>1.977999999999999</v>
+        <v>7.4151</v>
       </c>
       <c r="F4" t="n">
-        <v>9.8002</v>
+        <v>-0.01610000000000023</v>
       </c>
       <c r="G4" t="n">
-        <v>-6.6127</v>
+        <v>-6.1937</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.577</v>
+        <v>-3.6909</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.035599999999999</v>
+        <v>-2.5027</v>
       </c>
       <c r="J4" t="n">
-        <v>8.811400000000001</v>
+        <v>8.4613</v>
       </c>
       <c r="K4" t="n">
-        <v>7.2114</v>
+        <v>6.083600000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6001</v>
+        <v>2.3774</v>
       </c>
       <c r="M4" t="n">
-        <v>-15.424</v>
+        <v>-14.6548</v>
       </c>
       <c r="N4" t="n">
-        <v>-8.788399999999999</v>
+        <v>-9.7746</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.635899999999999</v>
+        <v>-4.88</v>
       </c>
       <c r="P4" t="n">
-        <v>11.3416</v>
+        <v>18.4385</v>
       </c>
       <c r="Q4" t="n">
-        <v>-14.2905</v>
+        <v>-7.7395</v>
       </c>
       <c r="R4" t="n">
-        <v>25.6322</v>
+        <v>26.1779</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4535</v>
+        <v>2.6975</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9651</v>
+        <v>6.377400000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4883</v>
+        <v>-3.6802</v>
       </c>
       <c r="V4" t="n">
-        <v>4.595499999999999</v>
+        <v>-7.5436</v>
       </c>
       <c r="W4" t="n">
-        <v>6.4917</v>
+        <v>0.3156</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8962</v>
+        <v>-7.8591</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7985</v>
+        <v>0.5848</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.09299999999999997</v>
+        <v>-0.2788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8915</v>
+        <v>0.8636</v>
       </c>
       <c r="G5" t="n">
-        <v>-9.0846</v>
+        <v>0.1435</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.5035</v>
+        <v>-0.1724</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.5811</v>
+        <v>0.3159</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7078000000000003</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9069</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.1988</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-9.7925</v>
+        <v>0.1435</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.4104</v>
+        <v>-0.1724</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.3826</v>
+        <v>0.3159</v>
       </c>
       <c r="P5" t="n">
-        <v>12.476</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-7.485500000000001</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>19.9614</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>3.398</v>
+        <v>-0.0139</v>
       </c>
       <c r="T5" t="n">
-        <v>6.524</v>
+        <v>-0.2788</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.1259</v>
+        <v>0.2649</v>
       </c>
       <c r="V5" t="n">
-        <v>-5.990600000000001</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.1513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>A. LIMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5810999999999999</v>
+        <v>-0.3928000000000003</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2782</v>
+        <v>-0.786</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8594000000000001</v>
+        <v>0.3931</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1414</v>
+        <v>-1.401</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1732</v>
+        <v>-1.1287</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3145</v>
+        <v>-0.2721999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.2183000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.1067000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.1117</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1414</v>
+        <v>-1.6194</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1732</v>
+        <v>-1.2355</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3145</v>
+        <v>-0.384</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0139</v>
+        <v>2.8472</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2782</v>
+        <v>2.2524</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2643</v>
+        <v>0.5949</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.4732999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6310999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LIMA</t>
+          <t>S. DE SOUSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4177000000000004</v>
+        <v>-1.7352</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7746</v>
+        <v>6.4269</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3569</v>
+        <v>-8.1623</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4098</v>
+        <v>1.1856</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1299</v>
+        <v>2.1723</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2798999999999999</v>
+        <v>-0.9865999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2260000000000001</v>
+        <v>6.161</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1140000000000001</v>
+        <v>5.193</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1119</v>
+        <v>0.9681</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6357</v>
+        <v>-4.9751</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2439</v>
+        <v>-3.0207</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3918</v>
+        <v>-1.9548</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.361</v>
+        <v>-3.869800000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4025</v>
+        <v>-14.5685</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>10.6988</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8352</v>
+        <v>10.4498</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2412</v>
+        <v>9.357200000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.594</v>
+        <v>1.0925</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4821</v>
+        <v>-9.5009</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>5.4772</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6429</v>
+        <v>-14.9781</v>
       </c>
     </row>
     <row r="8">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.07</v>
+        <v>-2.2216</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9786</v>
+        <v>-1.2733</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0914</v>
+        <v>-0.9482</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9676</v>
+        <v>-2.122</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0346</v>
+        <v>-0.5311</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0023</v>
+        <v>-1.5909</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7517</v>
+        <v>-0.976</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0346</v>
+        <v>-0.1863</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2159</v>
+        <v>-1.1459</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.3447</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2159</v>
+        <v>-0.8012</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2852</v>
+        <v>0.2858</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.0697</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2852</v>
+        <v>0.3555</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. DE SOUSA</t>
+          <t>S. GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.817800000000001</v>
+        <v>-3.8874</v>
       </c>
       <c r="E9" t="n">
-        <v>6.5876</v>
+        <v>-3.1278</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.4054</v>
+        <v>-0.7595999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1463</v>
+        <v>0.843</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1905</v>
+        <v>-0.4743</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0445</v>
+        <v>1.3173</v>
       </c>
       <c r="J9" t="n">
-        <v>6.2705</v>
+        <v>1.3094</v>
       </c>
       <c r="K9" t="n">
-        <v>5.3001</v>
+        <v>-0.3587</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9702999999999999</v>
+        <v>1.668</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.1243</v>
+        <v>-0.4661</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.1094</v>
+        <v>-0.1155</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0146</v>
+        <v>-0.3507000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.8562</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q9" t="n">
-        <v>-14.5174</v>
+        <v>-4.5527</v>
       </c>
       <c r="R9" t="n">
-        <v>10.6612</v>
+        <v>1.821</v>
       </c>
       <c r="S9" t="n">
-        <v>10.411</v>
+        <v>-0.207</v>
       </c>
       <c r="T9" t="n">
-        <v>9.3064</v>
+        <v>0.1155000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1046</v>
+        <v>-0.3224000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-9.519</v>
+        <v>-1.792</v>
       </c>
       <c r="W9" t="n">
-        <v>5.528</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-15.047</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. GARCIA</t>
+          <t>Y. NZOSA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9033</v>
+        <v>-4.015600000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1017</v>
+        <v>-3.701000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8018000000000001</v>
+        <v>-0.3146</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8256000000000001</v>
+        <v>-0.3484000000000003</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4806</v>
+        <v>-1.6035</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3062</v>
+        <v>1.2553</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3232</v>
+        <v>5.937799999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3534</v>
+        <v>4.4636</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6765</v>
+        <v>1.474</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4975</v>
+        <v>-6.2862</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1272</v>
+        <v>-6.0671</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3703000000000001</v>
+        <v>-0.2188999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.722</v>
+        <v>8.649899999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.5367</v>
+        <v>-12.9751</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8146</v>
+        <v>21.6251</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2071</v>
+        <v>-0.0515000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.112</v>
+        <v>-0.4917999999999997</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3190999999999999</v>
+        <v>0.4406</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7997</v>
+        <v>-12.2655</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.8282</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7997</v>
+        <v>-16.0937</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SHACKELFORD</t>
+          <t>D. DIEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5565</v>
+        <v>-4.2434</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.870200000000001</v>
+        <v>-11.8989</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3136</v>
+        <v>7.655600000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.1555</v>
+        <v>-22.7704</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.7082</v>
+        <v>-8.605699999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4474</v>
+        <v>-14.1649</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.4305</v>
+        <v>2.3566</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.8795</v>
+        <v>6.5031</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5511</v>
+        <v>-4.1467</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7249</v>
+        <v>-25.127</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8288</v>
+        <v>-15.1089</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1037</v>
+        <v>-10.0182</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7219</v>
+        <v>15.2513</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2684</v>
+        <v>-19.3489</v>
       </c>
       <c r="R11" t="n">
-        <v>4.9903</v>
+        <v>34.5999</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.898099999999999</v>
+        <v>1.2059</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.8388</v>
+        <v>-0.7561999999999997</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.05930000000000002</v>
+        <v>1.962</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2248999999999999</v>
+        <v>2.07</v>
       </c>
       <c r="W11" t="n">
-        <v>2.6675</v>
+        <v>5.8492</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8925</v>
+        <v>-3.7793</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>28</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6161</v>
+        <v>-5.8201</v>
       </c>
       <c r="E12" t="n">
-        <v>5.2246</v>
+        <v>-3.6104</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.8405</v>
+        <v>-2.2099</v>
       </c>
       <c r="G12" t="n">
-        <v>8.721800000000002</v>
+        <v>-16.2426</v>
       </c>
       <c r="H12" t="n">
-        <v>24.1727</v>
+        <v>-4.4573</v>
       </c>
       <c r="I12" t="n">
-        <v>-15.4512</v>
+        <v>-11.7851</v>
       </c>
       <c r="J12" t="n">
-        <v>45.1996</v>
+        <v>-1.658000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>42.7194</v>
+        <v>3.0908</v>
       </c>
       <c r="L12" t="n">
-        <v>2.4803</v>
+        <v>-4.748699999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-36.4779</v>
+        <v>-14.5845</v>
       </c>
       <c r="N12" t="n">
-        <v>-18.5466</v>
+        <v>-7.5484</v>
       </c>
       <c r="O12" t="n">
-        <v>-17.9313</v>
+        <v>-7.0363</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5877</v>
+        <v>20.0317</v>
       </c>
       <c r="Q12" t="n">
-        <v>-56.0279</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>54.4399</v>
+        <v>24.5844</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2026</v>
+        <v>-0.3229999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.489400000000001</v>
+        <v>2.2848</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7130999999999998</v>
+        <v>-2.6075</v>
       </c>
       <c r="V12" t="n">
-        <v>-15.9525</v>
+        <v>-9.2865</v>
       </c>
       <c r="W12" t="n">
-        <v>13.5631</v>
+        <v>0.3156</v>
       </c>
       <c r="X12" t="n">
-        <v>-29.5155</v>
+        <v>-9.6021</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Y. NZOSA</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6571</v>
+        <v>-6.788000000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9857</v>
+        <v>2.583999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.6713</v>
+        <v>-9.3718</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0951</v>
+        <v>1.887499999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>2.878</v>
+        <v>18.0673</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7829</v>
+        <v>-16.1798</v>
       </c>
       <c r="J13" t="n">
-        <v>5.9893</v>
+        <v>43.6242</v>
       </c>
       <c r="K13" t="n">
-        <v>5.957400000000001</v>
+        <v>41.8018</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03179999999999997</v>
+        <v>1.8222</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.894</v>
+        <v>-41.7365</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.0796</v>
+        <v>-23.7347</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8147</v>
+        <v>-18.0019</v>
       </c>
       <c r="P13" t="n">
-        <v>7.2586</v>
+        <v>-1.820999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.6612</v>
+        <v>-66.9237</v>
       </c>
       <c r="R13" t="n">
-        <v>17.9198</v>
+        <v>65.1026</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0108</v>
+        <v>7.6549</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0099</v>
+        <v>6.2849</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0006</v>
+        <v>1.3699</v>
       </c>
       <c r="V13" t="n">
-        <v>-12.0002</v>
+        <v>-14.5088</v>
       </c>
       <c r="W13" t="n">
-        <v>3.696</v>
+        <v>19.5986</v>
       </c>
       <c r="X13" t="n">
-        <v>-15.6961</v>
+        <v>-34.1076</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>J. TABOADA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.7638</v>
+        <v>-8.5632</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.7181</v>
+        <v>-0.8222</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0458</v>
+        <v>-7.7409</v>
       </c>
       <c r="G14" t="n">
-        <v>-16.2627</v>
+        <v>-5.3568</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.9004</v>
+        <v>-2.415</v>
       </c>
       <c r="I14" t="n">
-        <v>-12.3624</v>
+        <v>-2.9416</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.6715</v>
+        <v>-0.6506000000000003</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6763</v>
+        <v>-0.7906</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.3477</v>
+        <v>0.1400999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.591</v>
+        <v>-4.7063</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.576</v>
+        <v>-1.6245</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.0147</v>
+        <v>-3.0819</v>
       </c>
       <c r="P14" t="n">
-        <v>17.0124</v>
+        <v>4.3251</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.5366</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>21.5491</v>
+        <v>5.690899999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3986</v>
+        <v>-0.8367999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1685</v>
+        <v>0.6493</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.77</v>
+        <v>-1.4859</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.9123</v>
+        <v>-6.6947</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3214</v>
+        <v>0.5447</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.233700000000001</v>
+        <v>-7.2394</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. TABOADA</t>
+          <t>M. HEIDEGGER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.635199999999999</v>
+        <v>-9.5745</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1534</v>
+        <v>-2.156899999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.4818</v>
+        <v>-7.4173</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.6725</v>
+        <v>9.7462</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.8656</v>
+        <v>-0.09260000000000007</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.8067</v>
+        <v>9.838899999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.6756</v>
+        <v>19.6666</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.4382</v>
+        <v>7.2514</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2374000000000001</v>
+        <v>12.4151</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.9968</v>
+        <v>-9.920400000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4275</v>
+        <v>-7.3442</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.5694</v>
+        <v>-2.5763</v>
       </c>
       <c r="P15" t="n">
-        <v>3.6294</v>
+        <v>-10.2435</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-22.5356</v>
       </c>
       <c r="R15" t="n">
-        <v>3.8562</v>
+        <v>12.2921</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4217</v>
+        <v>-8.2506</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2026</v>
+        <v>-5.5957</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.6244</v>
+        <v>-2.6548</v>
       </c>
       <c r="V15" t="n">
-        <v>-6.1704</v>
+        <v>-0.8262</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5463</v>
+        <v>6.3077</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.7167</v>
+        <v>-7.133900000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HEIDEGGER</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>-9.714199999999998</v>
+        <v>-10.528</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.146100000000001</v>
+        <v>-0.474499999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.568</v>
+        <v>-10.0535</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0916</v>
+        <v>19.9101</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7850000000000001</v>
+        <v>-8.2456</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3068</v>
+        <v>28.156</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5623</v>
+        <v>44.4473</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0668</v>
+        <v>14.0206</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4954000000000001</v>
+        <v>30.427</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.654</v>
+        <v>-24.5375</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.8518</v>
+        <v>-22.2663</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8021</v>
+        <v>-2.2714</v>
       </c>
       <c r="P16" t="n">
-        <v>-4.3098</v>
+        <v>-12.7475</v>
       </c>
       <c r="Q16" t="n">
-        <v>-8.392800000000001</v>
+        <v>-70.56570000000001</v>
       </c>
       <c r="R16" t="n">
-        <v>4.083</v>
+        <v>57.8185</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.2556</v>
+        <v>-13.6708</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3155</v>
+        <v>-6.454</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9400999999999999</v>
+        <v>-7.2168</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.057</v>
+        <v>-4.0197</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>32.0979</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.057</v>
+        <v>-36.1174</v>
       </c>
     </row>
     <row r="17">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>-16.0003</v>
+        <v>-13.1959</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.5616</v>
+        <v>2.3882</v>
       </c>
       <c r="F17" t="n">
-        <v>-12.439</v>
+        <v>-15.5839</v>
       </c>
       <c r="G17" t="n">
-        <v>-11.5437</v>
+        <v>-11.5128</v>
       </c>
       <c r="H17" t="n">
-        <v>-11.7562</v>
+        <v>-12.2248</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2124999999999998</v>
+        <v>0.7124999999999995</v>
       </c>
       <c r="J17" t="n">
-        <v>9.773199999999999</v>
+        <v>12.0142</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0115</v>
+        <v>3.9335</v>
       </c>
       <c r="L17" t="n">
-        <v>7.7619</v>
+        <v>8.080500000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-21.317</v>
+        <v>-23.5268</v>
       </c>
       <c r="N17" t="n">
-        <v>-13.7674</v>
+        <v>-16.1583</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.5496</v>
+        <v>-7.3684</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3612</v>
+        <v>3.6423</v>
       </c>
       <c r="Q17" t="n">
-        <v>-34.0251</v>
+        <v>-35.5108</v>
       </c>
       <c r="R17" t="n">
-        <v>35.3862</v>
+        <v>39.1531</v>
       </c>
       <c r="S17" t="n">
-        <v>6.8572</v>
+        <v>8.2447</v>
       </c>
       <c r="T17" t="n">
-        <v>7.2559</v>
+        <v>9.7271</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3986000000000001</v>
+        <v>-1.4826</v>
       </c>
       <c r="V17" t="n">
-        <v>-12.6747</v>
+        <v>-13.5698</v>
       </c>
       <c r="W17" t="n">
-        <v>13.4342</v>
+        <v>16.1579</v>
       </c>
       <c r="X17" t="n">
-        <v>-26.1088</v>
+        <v>-29.7269</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>J. SHACKELFORD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.3666</v>
+        <v>-16.2279</v>
       </c>
       <c r="E18" t="n">
-        <v>-13.7704</v>
+        <v>-15.251</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5957</v>
+        <v>-0.9767999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>5.467899999999999</v>
+        <v>-9.9398</v>
       </c>
       <c r="H18" t="n">
-        <v>-9.995000000000001</v>
+        <v>-7.5787</v>
       </c>
       <c r="I18" t="n">
-        <v>15.4626</v>
+        <v>-2.3612</v>
       </c>
       <c r="J18" t="n">
-        <v>21.3796</v>
+        <v>-7.952900000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>4.735399999999999</v>
+        <v>-3.6981</v>
       </c>
       <c r="L18" t="n">
-        <v>16.6442</v>
+        <v>-4.254799999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-15.9116</v>
+        <v>-1.9869</v>
       </c>
       <c r="N18" t="n">
-        <v>-14.7301</v>
+        <v>-3.8806</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1813</v>
+        <v>1.8936</v>
       </c>
       <c r="P18" t="n">
-        <v>-8.6198</v>
+        <v>1.3657</v>
       </c>
       <c r="Q18" t="n">
-        <v>-54.2132</v>
+        <v>-7.2842</v>
       </c>
       <c r="R18" t="n">
-        <v>45.5935</v>
+        <v>8.65</v>
       </c>
       <c r="S18" t="n">
-        <v>-9.563800000000001</v>
+        <v>-4.4716</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.3338</v>
+        <v>-4.071</v>
       </c>
       <c r="U18" t="n">
-        <v>-5.2304</v>
+        <v>-0.4005000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.6511</v>
+        <v>-3.1821</v>
       </c>
       <c r="W18" t="n">
-        <v>23.3966</v>
+        <v>4.0573</v>
       </c>
       <c r="X18" t="n">
-        <v>-27.0475</v>
+        <v>-7.2394</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>-25.8382</v>
+        <v>-26.0981</v>
       </c>
       <c r="E19" t="n">
-        <v>-13.4941</v>
+        <v>-14.568</v>
       </c>
       <c r="F19" t="n">
-        <v>-12.3442</v>
+        <v>-11.5298</v>
       </c>
       <c r="G19" t="n">
-        <v>-16.1206</v>
+        <v>-16.338</v>
       </c>
       <c r="H19" t="n">
-        <v>-15.7892</v>
+        <v>-15.8641</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3317000000000005</v>
+        <v>-0.4739999999999993</v>
       </c>
       <c r="J19" t="n">
-        <v>14.7691</v>
+        <v>13.9789</v>
       </c>
       <c r="K19" t="n">
-        <v>5.944</v>
+        <v>5.5503</v>
       </c>
       <c r="L19" t="n">
-        <v>8.825100000000001</v>
+        <v>8.4285</v>
       </c>
       <c r="M19" t="n">
-        <v>-30.8897</v>
+        <v>-30.3171</v>
       </c>
       <c r="N19" t="n">
-        <v>-21.7332</v>
+        <v>-21.4144</v>
       </c>
       <c r="O19" t="n">
-        <v>-9.156700000000001</v>
+        <v>-8.9023</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9072999999999993</v>
+        <v>-0.9104999999999996</v>
       </c>
       <c r="Q19" t="n">
-        <v>-48.3155</v>
+        <v>-48.4856</v>
       </c>
       <c r="R19" t="n">
-        <v>47.4081</v>
+        <v>47.5749</v>
       </c>
       <c r="S19" t="n">
-        <v>-13.3672</v>
+        <v>-13.4101</v>
       </c>
       <c r="T19" t="n">
-        <v>-11.0571</v>
+        <v>-11.0549</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.31</v>
+        <v>-2.3552</v>
       </c>
       <c r="V19" t="n">
-        <v>4.5568</v>
+        <v>4.5608</v>
       </c>
       <c r="W19" t="n">
-        <v>31.1095</v>
+        <v>30.9936</v>
       </c>
       <c r="X19" t="n">
-        <v>-26.5523</v>
+        <v>-26.4324</v>
       </c>
     </row>
     <row r="20">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>-31.5683</v>
+        <v>-41.4988</v>
       </c>
       <c r="E20" t="n">
-        <v>-27.1495</v>
+        <v>-33.9211</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.4192</v>
+        <v>-7.577999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-18.23</v>
+        <v>-27.2453</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.7235</v>
+        <v>-11.3528</v>
       </c>
       <c r="I20" t="n">
-        <v>-12.5063</v>
+        <v>-15.8924</v>
       </c>
       <c r="J20" t="n">
-        <v>15.2289</v>
+        <v>14.071</v>
       </c>
       <c r="K20" t="n">
-        <v>5.8295</v>
+        <v>6.187799999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>9.399699999999999</v>
+        <v>7.883299999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-33.4589</v>
+        <v>-41.3161</v>
       </c>
       <c r="N20" t="n">
-        <v>-11.5531</v>
+        <v>-17.5402</v>
       </c>
       <c r="O20" t="n">
-        <v>-21.9061</v>
+        <v>-23.7756</v>
       </c>
       <c r="P20" t="n">
-        <v>6.3513</v>
+        <v>6.6014</v>
       </c>
       <c r="Q20" t="n">
-        <v>-42.8715</v>
+        <v>-50.3066</v>
       </c>
       <c r="R20" t="n">
-        <v>49.2227</v>
+        <v>56.9082</v>
       </c>
       <c r="S20" t="n">
-        <v>-16.8101</v>
+        <v>-16.2533</v>
       </c>
       <c r="T20" t="n">
-        <v>-14.3869</v>
+        <v>-13.5837</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.4232</v>
+        <v>-2.6696</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.879599999999999</v>
+        <v>-4.601999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>14.88</v>
+        <v>15.8986</v>
       </c>
       <c r="X20" t="n">
-        <v>-17.7595</v>
+        <v>-20.5005</v>
       </c>
     </row>
     <row r="21">
@@ -2044,70 +2044,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D21" t="n">
-        <v>-45.3709</v>
+        <v>-46.919</v>
       </c>
       <c r="E21" t="n">
-        <v>-33.9578</v>
+        <v>-44.2457</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.413</v>
+        <v>-2.672599999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-65.08029999999999</v>
+        <v>-74.18089999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-23.154</v>
+        <v>-31.3438</v>
       </c>
       <c r="I21" t="n">
-        <v>-41.9259</v>
+        <v>-42.8372</v>
       </c>
       <c r="J21" t="n">
-        <v>-23.7179</v>
+        <v>-28.3275</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.233</v>
+        <v>-7.104799999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-20.4848</v>
+        <v>-21.2232</v>
       </c>
       <c r="M21" t="n">
-        <v>-41.3627</v>
+        <v>-45.8535</v>
       </c>
       <c r="N21" t="n">
-        <v>-19.9214</v>
+        <v>-24.2391</v>
       </c>
       <c r="O21" t="n">
-        <v>-21.4414</v>
+        <v>-21.6142</v>
       </c>
       <c r="P21" t="n">
-        <v>12.0223</v>
+        <v>15.4792</v>
       </c>
       <c r="Q21" t="n">
-        <v>-47.1815</v>
+        <v>-54.4038</v>
       </c>
       <c r="R21" t="n">
-        <v>59.2038</v>
+        <v>69.88289999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>12.4237</v>
+        <v>14.5863</v>
       </c>
       <c r="T21" t="n">
-        <v>8.659700000000001</v>
+        <v>9.168100000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>3.7641</v>
+        <v>5.418</v>
       </c>
       <c r="V21" t="n">
-        <v>-4.7364</v>
+        <v>-2.802500000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>28.2818</v>
+        <v>29.3174</v>
       </c>
       <c r="X21" t="n">
-        <v>-33.0183</v>
+        <v>-32.1202</v>
       </c>
     </row>
     <row r="22">
@@ -2122,70 +2122,70 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>-123.9332</v>
+        <v>-133.4014</v>
       </c>
       <c r="E22" t="n">
-        <v>-65.6832</v>
+        <v>-65.80720000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-58.2505</v>
+        <v>-67.59259999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-152.095</v>
+        <v>-176.7502</v>
       </c>
       <c r="H22" t="n">
-        <v>-37.3353</v>
+        <v>-81.21419999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-114.7604</v>
+        <v>-95.53399999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>158.1027</v>
+        <v>204.3184</v>
       </c>
       <c r="K22" t="n">
-        <v>135.2789</v>
+        <v>148.217</v>
       </c>
       <c r="L22" t="n">
-        <v>22.82449999999999</v>
+        <v>56.1001</v>
       </c>
       <c r="M22" t="n">
-        <v>-310.1975</v>
+        <v>-381.0674</v>
       </c>
       <c r="N22" t="n">
-        <v>-172.6132</v>
+        <v>-229.4325</v>
       </c>
       <c r="O22" t="n">
-        <v>-137.5853</v>
+        <v>-151.6352</v>
       </c>
       <c r="P22" t="n">
-        <v>72.58690000000001</v>
+        <v>85.36250000000003</v>
       </c>
       <c r="Q22" t="n">
-        <v>-442.3253000000001</v>
+        <v>-533.797</v>
       </c>
       <c r="R22" t="n">
-        <v>514.912</v>
+        <v>619.1587999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>7.122599999999998</v>
+        <v>9.880700000000003</v>
       </c>
       <c r="T22" t="n">
-        <v>17.3192</v>
+        <v>23.8404</v>
       </c>
       <c r="U22" t="n">
-        <v>-10.1968</v>
+        <v>-13.9596</v>
       </c>
       <c r="V22" t="n">
-        <v>-51.5474</v>
+        <v>-51.8922</v>
       </c>
       <c r="W22" t="n">
-        <v>201.2189</v>
+        <v>239.831</v>
       </c>
       <c r="X22" t="n">
-        <v>-252.7659</v>
+        <v>-291.7219</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Recoletas Salud San Pablo Burgos.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Recoletas Salud San Pablo Burgos.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D2" t="n">
-        <v>40.6322</v>
+        <v>35.7295</v>
       </c>
       <c r="E2" t="n">
-        <v>34.2506</v>
+        <v>29.9179</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3813</v>
+        <v>5.8118</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.8754</v>
+        <v>-11.939</v>
       </c>
       <c r="H2" t="n">
-        <v>2.439499999999999</v>
+        <v>5.888</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.3146</v>
+        <v>-17.8267</v>
       </c>
       <c r="J2" t="n">
-        <v>33.223</v>
+        <v>38.4138</v>
       </c>
       <c r="K2" t="n">
-        <v>21.2854</v>
+        <v>34.8839</v>
       </c>
       <c r="L2" t="n">
-        <v>11.9375</v>
+        <v>3.5297</v>
       </c>
       <c r="M2" t="n">
-        <v>-38.0985</v>
+        <v>-50.3523</v>
       </c>
       <c r="N2" t="n">
-        <v>-18.8461</v>
+        <v>-28.9963</v>
       </c>
       <c r="O2" t="n">
-        <v>-19.2522</v>
+        <v>-21.3564</v>
       </c>
       <c r="P2" t="n">
-        <v>8.194699999999999</v>
+        <v>16.8447</v>
       </c>
       <c r="Q2" t="n">
-        <v>-49.8513</v>
+        <v>-59.1845</v>
       </c>
       <c r="R2" t="n">
-        <v>58.0458</v>
+        <v>76.0287</v>
       </c>
       <c r="S2" t="n">
-        <v>38.0982</v>
+        <v>-2.664100000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>30.3486</v>
+        <v>2.3051</v>
       </c>
       <c r="U2" t="n">
-        <v>7.7495</v>
+        <v>-4.9694</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7853000000000003</v>
+        <v>33.4877</v>
       </c>
       <c r="W2" t="n">
-        <v>20.5305</v>
+        <v>48.3832</v>
       </c>
       <c r="X2" t="n">
-        <v>-21.3155</v>
+        <v>-14.8955</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>19.6926</v>
+        <v>17.1515</v>
       </c>
       <c r="E3" t="n">
-        <v>17.2436</v>
+        <v>15.0905</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4491</v>
+        <v>2.0606</v>
       </c>
       <c r="G3" t="n">
-        <v>-11.939</v>
+        <v>-4.8754</v>
       </c>
       <c r="H3" t="n">
-        <v>5.888</v>
+        <v>2.439499999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-17.8267</v>
+        <v>-7.3146</v>
       </c>
       <c r="J3" t="n">
-        <v>38.4138</v>
+        <v>33.223</v>
       </c>
       <c r="K3" t="n">
-        <v>34.8839</v>
+        <v>21.2854</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5297</v>
+        <v>11.9375</v>
       </c>
       <c r="M3" t="n">
-        <v>-50.3523</v>
+        <v>-38.0985</v>
       </c>
       <c r="N3" t="n">
-        <v>-28.9963</v>
+        <v>-18.8461</v>
       </c>
       <c r="O3" t="n">
-        <v>-21.3564</v>
+        <v>-19.2522</v>
       </c>
       <c r="P3" t="n">
-        <v>16.8447</v>
+        <v>8.194699999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-59.1845</v>
+        <v>-49.8513</v>
       </c>
       <c r="R3" t="n">
-        <v>76.0287</v>
+        <v>58.0458</v>
       </c>
       <c r="S3" t="n">
-        <v>-18.701</v>
+        <v>14.6169</v>
       </c>
       <c r="T3" t="n">
-        <v>-10.3691</v>
+        <v>11.1887</v>
       </c>
       <c r="U3" t="n">
-        <v>-8.331899999999999</v>
+        <v>3.4283</v>
       </c>
       <c r="V3" t="n">
-        <v>33.4877</v>
+        <v>-0.7853000000000003</v>
       </c>
       <c r="W3" t="n">
-        <v>48.3832</v>
+        <v>20.5305</v>
       </c>
       <c r="X3" t="n">
-        <v>-14.8955</v>
+        <v>-21.3155</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>7.3985</v>
+        <v>7.9633</v>
       </c>
       <c r="E4" t="n">
-        <v>7.4151</v>
+        <v>5.6804</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01610000000000023</v>
+        <v>2.2834</v>
       </c>
       <c r="G4" t="n">
         <v>-6.1937</v>
@@ -766,13 +766,13 @@
         <v>26.1779</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6975</v>
+        <v>3.2628</v>
       </c>
       <c r="T4" t="n">
-        <v>6.377400000000001</v>
+        <v>4.6428</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.6802</v>
+        <v>-1.3804</v>
       </c>
       <c r="V4" t="n">
         <v>-7.5436</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5848</v>
+        <v>0.5509999999999988</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2788</v>
+        <v>6.521199999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8636</v>
+        <v>-5.9704</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1435</v>
+        <v>19.9101</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1724</v>
+        <v>-8.2456</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3159</v>
+        <v>28.156</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>44.4473</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>14.0206</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>30.427</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1435</v>
+        <v>-24.5375</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1724</v>
+        <v>-22.2663</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3159</v>
+        <v>-2.2714</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4553</v>
+        <v>-12.7475</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-70.56570000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4553</v>
+        <v>57.8185</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0139</v>
+        <v>-2.5923</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2788</v>
+        <v>0.5415999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2649</v>
+        <v>-3.1336</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-4.0197</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>32.0979</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-36.1174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LIMA</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3928000000000003</v>
+        <v>0.4593</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.786</v>
+        <v>-0.2788</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3931</v>
+        <v>0.7382</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.401</v>
+        <v>0.1435</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1287</v>
+        <v>-0.1724</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2721999999999999</v>
+        <v>0.3159</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2183000000000001</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1067000000000001</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1117</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6194</v>
+        <v>0.1435</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2355</v>
+        <v>-0.1724</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.384</v>
+        <v>0.3159</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3658</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4145</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0487</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8472</v>
+        <v>-0.1394</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2524</v>
+        <v>-0.2788</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5949</v>
+        <v>0.1394</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4732999999999999</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6310999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. DE SOUSA</t>
+          <t>A. LIMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7352</v>
+        <v>-1.6331</v>
       </c>
       <c r="E7" t="n">
-        <v>6.4269</v>
+        <v>-1.9007</v>
       </c>
       <c r="F7" t="n">
-        <v>-8.1623</v>
+        <v>0.2677</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1856</v>
+        <v>-1.401</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1723</v>
+        <v>-1.1287</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9865999999999999</v>
+        <v>-0.2721999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>6.161</v>
+        <v>0.2183000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>5.193</v>
+        <v>0.1067000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9681</v>
+        <v>0.1117</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.9751</v>
+        <v>-1.6194</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.0207</v>
+        <v>-1.2355</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9548</v>
+        <v>-0.384</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.869800000000001</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-14.5685</v>
+        <v>-3.4145</v>
       </c>
       <c r="R7" t="n">
-        <v>10.6988</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>10.4498</v>
+        <v>1.607</v>
       </c>
       <c r="T7" t="n">
-        <v>9.357200000000001</v>
+        <v>1.1377</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0925</v>
+        <v>0.4694</v>
       </c>
       <c r="V7" t="n">
-        <v>-9.5009</v>
+        <v>-0.4732999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>5.4772</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.9781</v>
+        <v>-0.6310999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2216</v>
+        <v>-2.0788</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2733</v>
+        <v>-1.0365</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9482</v>
+        <v>-1.0423</v>
       </c>
       <c r="G8" t="n">
         <v>-2.122</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2858</v>
+        <v>0.4285</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0697</v>
+        <v>0.1671</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3555</v>
+        <v>0.2614</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1578</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. GARCIA</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8874</v>
+        <v>-2.230700000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1278</v>
+        <v>-3.5408</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7595999999999999</v>
+        <v>1.3097</v>
       </c>
       <c r="G9" t="n">
-        <v>0.843</v>
+        <v>-16.2426</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4743</v>
+        <v>-4.4573</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3173</v>
+        <v>-11.7851</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3094</v>
+        <v>-1.658000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3587</v>
+        <v>3.0908</v>
       </c>
       <c r="L9" t="n">
-        <v>1.668</v>
+        <v>-4.748699999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4661</v>
+        <v>-14.5845</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1155</v>
+        <v>-7.5484</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3507000000000001</v>
+        <v>-7.0363</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7316</v>
+        <v>20.0317</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.5527</v>
+        <v>-4.5526</v>
       </c>
       <c r="R9" t="n">
-        <v>1.821</v>
+        <v>24.5844</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.207</v>
+        <v>3.2666</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1155000000000001</v>
+        <v>2.3544</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3224000000000001</v>
+        <v>0.9120999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.792</v>
+        <v>-9.2865</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3156</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.792</v>
+        <v>-9.6021</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. NZOSA</t>
+          <t>D. DIEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.015600000000001</v>
+        <v>-2.5543</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.701000000000001</v>
+        <v>-9.3065</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3146</v>
+        <v>6.752300000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3484000000000003</v>
+        <v>-22.7704</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6035</v>
+        <v>-8.605699999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2553</v>
+        <v>-14.1649</v>
       </c>
       <c r="J10" t="n">
-        <v>5.937799999999999</v>
+        <v>2.3566</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4636</v>
+        <v>6.5031</v>
       </c>
       <c r="L10" t="n">
-        <v>1.474</v>
+        <v>-4.1467</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.2862</v>
+        <v>-25.127</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.0671</v>
+        <v>-15.1089</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2188999999999999</v>
+        <v>-10.0182</v>
       </c>
       <c r="P10" t="n">
-        <v>8.649899999999999</v>
+        <v>15.2513</v>
       </c>
       <c r="Q10" t="n">
-        <v>-12.9751</v>
+        <v>-19.3489</v>
       </c>
       <c r="R10" t="n">
-        <v>21.6251</v>
+        <v>34.5999</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0515000000000001</v>
+        <v>2.8951</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4917999999999997</v>
+        <v>1.8361</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4406</v>
+        <v>1.0589</v>
       </c>
       <c r="V10" t="n">
-        <v>-12.2655</v>
+        <v>2.07</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8282</v>
+        <v>5.8492</v>
       </c>
       <c r="X10" t="n">
-        <v>-16.0937</v>
+        <v>-3.7793</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. DIEZ</t>
+          <t>Y. NZOSA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2434</v>
+        <v>-3.1839</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.8989</v>
+        <v>-2.9972</v>
       </c>
       <c r="F11" t="n">
-        <v>7.655600000000001</v>
+        <v>-0.1872</v>
       </c>
       <c r="G11" t="n">
-        <v>-22.7704</v>
+        <v>-0.3484000000000003</v>
       </c>
       <c r="H11" t="n">
-        <v>-8.605699999999999</v>
+        <v>-1.6035</v>
       </c>
       <c r="I11" t="n">
-        <v>-14.1649</v>
+        <v>1.2553</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3566</v>
+        <v>5.937799999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>6.5031</v>
+        <v>4.4636</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.1467</v>
+        <v>1.474</v>
       </c>
       <c r="M11" t="n">
-        <v>-25.127</v>
+        <v>-6.2862</v>
       </c>
       <c r="N11" t="n">
-        <v>-15.1089</v>
+        <v>-6.0671</v>
       </c>
       <c r="O11" t="n">
-        <v>-10.0182</v>
+        <v>-0.2188999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>15.2513</v>
+        <v>8.649899999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-19.3489</v>
+        <v>-12.9751</v>
       </c>
       <c r="R11" t="n">
-        <v>34.5999</v>
+        <v>21.6251</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2059</v>
+        <v>0.7801000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7561999999999997</v>
+        <v>0.2118000000000002</v>
       </c>
       <c r="U11" t="n">
-        <v>1.962</v>
+        <v>0.5682</v>
       </c>
       <c r="V11" t="n">
-        <v>2.07</v>
+        <v>-12.2655</v>
       </c>
       <c r="W11" t="n">
-        <v>5.8492</v>
+        <v>3.8282</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.7793</v>
+        <v>-16.0937</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>M. HEIDEGGER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8201</v>
+        <v>-3.683699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6104</v>
+        <v>1.912199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2099</v>
+        <v>-5.596</v>
       </c>
       <c r="G12" t="n">
-        <v>-16.2426</v>
+        <v>9.7462</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.4573</v>
+        <v>-0.09260000000000007</v>
       </c>
       <c r="I12" t="n">
-        <v>-11.7851</v>
+        <v>9.838899999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.658000000000001</v>
+        <v>19.6666</v>
       </c>
       <c r="K12" t="n">
-        <v>3.0908</v>
+        <v>7.2514</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.748699999999999</v>
+        <v>12.4151</v>
       </c>
       <c r="M12" t="n">
-        <v>-14.5845</v>
+        <v>-9.920400000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.5484</v>
+        <v>-7.3442</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.0363</v>
+        <v>-2.5763</v>
       </c>
       <c r="P12" t="n">
-        <v>20.0317</v>
+        <v>-10.2435</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5526</v>
+        <v>-22.5356</v>
       </c>
       <c r="R12" t="n">
-        <v>24.5844</v>
+        <v>12.2921</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3229999999999999</v>
+        <v>-2.3601</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2848</v>
+        <v>-1.5266</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.6075</v>
+        <v>-0.8333999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-9.2865</v>
+        <v>-0.8262</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3156</v>
+        <v>6.3077</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.6021</v>
+        <v>-7.133900000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>S. GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.788000000000002</v>
+        <v>-4.4414</v>
       </c>
       <c r="E13" t="n">
-        <v>2.583999999999999</v>
+        <v>-3.8385</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.3718</v>
+        <v>-0.6028000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>1.887499999999998</v>
+        <v>0.843</v>
       </c>
       <c r="H13" t="n">
-        <v>18.0673</v>
+        <v>-0.4743</v>
       </c>
       <c r="I13" t="n">
-        <v>-16.1798</v>
+        <v>1.3173</v>
       </c>
       <c r="J13" t="n">
-        <v>43.6242</v>
+        <v>1.3094</v>
       </c>
       <c r="K13" t="n">
-        <v>41.8018</v>
+        <v>-0.3587</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8222</v>
+        <v>1.668</v>
       </c>
       <c r="M13" t="n">
-        <v>-41.7365</v>
+        <v>-0.4661</v>
       </c>
       <c r="N13" t="n">
-        <v>-23.7347</v>
+        <v>-0.1155</v>
       </c>
       <c r="O13" t="n">
-        <v>-18.0019</v>
+        <v>-0.3507000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.820999999999999</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q13" t="n">
-        <v>-66.9237</v>
+        <v>-4.5527</v>
       </c>
       <c r="R13" t="n">
-        <v>65.1026</v>
+        <v>1.821</v>
       </c>
       <c r="S13" t="n">
-        <v>7.6549</v>
+        <v>-0.7606999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>6.2849</v>
+        <v>-0.5951</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3699</v>
+        <v>-0.1655999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-14.5088</v>
+        <v>-1.792</v>
       </c>
       <c r="W13" t="n">
-        <v>19.5986</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-34.1076</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.5632</v>
+        <v>-7.9705</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8222</v>
+        <v>-1.1078</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.7409</v>
+        <v>-6.8628</v>
       </c>
       <c r="G14" t="n">
         <v>-5.3568</v>
@@ -1546,13 +1546,13 @@
         <v>5.690899999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8367999999999999</v>
+        <v>-0.2442</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6493</v>
+        <v>0.3636</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4859</v>
+        <v>-0.6079</v>
       </c>
       <c r="V14" t="n">
         <v>-6.6947</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. HEIDEGGER</t>
+          <t>S. DE SOUSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.5745</v>
+        <v>-8.637</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.156899999999999</v>
+        <v>0.7139000000000009</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.4173</v>
+        <v>-9.3508</v>
       </c>
       <c r="G15" t="n">
-        <v>9.7462</v>
+        <v>1.1856</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09260000000000007</v>
+        <v>2.1723</v>
       </c>
       <c r="I15" t="n">
-        <v>9.838899999999999</v>
+        <v>-0.9865999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>19.6666</v>
+        <v>6.161</v>
       </c>
       <c r="K15" t="n">
-        <v>7.2514</v>
+        <v>5.193</v>
       </c>
       <c r="L15" t="n">
-        <v>12.4151</v>
+        <v>0.9681</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.920400000000001</v>
+        <v>-4.9751</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.3442</v>
+        <v>-3.0207</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.5763</v>
+        <v>-1.9548</v>
       </c>
       <c r="P15" t="n">
-        <v>-10.2435</v>
+        <v>-3.869800000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-22.5356</v>
+        <v>-14.5685</v>
       </c>
       <c r="R15" t="n">
-        <v>12.2921</v>
+        <v>10.6988</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.2506</v>
+        <v>3.5478</v>
       </c>
       <c r="T15" t="n">
-        <v>-5.5957</v>
+        <v>3.6442</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.6548</v>
+        <v>-0.0963</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8262</v>
+        <v>-9.5009</v>
       </c>
       <c r="W15" t="n">
-        <v>6.3077</v>
+        <v>5.4772</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.133900000000001</v>
+        <v>-14.9781</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>-10.528</v>
+        <v>-11.5864</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.474499999999999</v>
+        <v>-1.157000000000002</v>
       </c>
       <c r="F16" t="n">
-        <v>-10.0535</v>
+        <v>-10.4296</v>
       </c>
       <c r="G16" t="n">
-        <v>19.9101</v>
+        <v>1.887499999999998</v>
       </c>
       <c r="H16" t="n">
-        <v>-8.2456</v>
+        <v>18.0673</v>
       </c>
       <c r="I16" t="n">
-        <v>28.156</v>
+        <v>-16.1798</v>
       </c>
       <c r="J16" t="n">
-        <v>44.4473</v>
+        <v>43.6242</v>
       </c>
       <c r="K16" t="n">
-        <v>14.0206</v>
+        <v>41.8018</v>
       </c>
       <c r="L16" t="n">
-        <v>30.427</v>
+        <v>1.8222</v>
       </c>
       <c r="M16" t="n">
-        <v>-24.5375</v>
+        <v>-41.7365</v>
       </c>
       <c r="N16" t="n">
-        <v>-22.2663</v>
+        <v>-23.7347</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2714</v>
+        <v>-18.0019</v>
       </c>
       <c r="P16" t="n">
-        <v>-12.7475</v>
+        <v>-1.820999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-70.56570000000001</v>
+        <v>-66.9237</v>
       </c>
       <c r="R16" t="n">
-        <v>57.8185</v>
+        <v>65.1026</v>
       </c>
       <c r="S16" t="n">
-        <v>-13.6708</v>
+        <v>2.8561</v>
       </c>
       <c r="T16" t="n">
-        <v>-6.454</v>
+        <v>2.5439</v>
       </c>
       <c r="U16" t="n">
-        <v>-7.2168</v>
+        <v>0.3122999999999997</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.0197</v>
+        <v>-14.5088</v>
       </c>
       <c r="W16" t="n">
-        <v>32.0979</v>
+        <v>19.5986</v>
       </c>
       <c r="X16" t="n">
-        <v>-36.1174</v>
+        <v>-34.1076</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. FISCHER</t>
+          <t>J. SHACKELFORD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>-13.1959</v>
+        <v>-11.9042</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3882</v>
+        <v>-12.248</v>
       </c>
       <c r="F17" t="n">
-        <v>-15.5839</v>
+        <v>0.3438999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-11.5128</v>
+        <v>-9.9398</v>
       </c>
       <c r="H17" t="n">
-        <v>-12.2248</v>
+        <v>-7.5787</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7124999999999995</v>
+        <v>-2.3612</v>
       </c>
       <c r="J17" t="n">
-        <v>12.0142</v>
+        <v>-7.952900000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9335</v>
+        <v>-3.6981</v>
       </c>
       <c r="L17" t="n">
-        <v>8.080500000000001</v>
+        <v>-4.254799999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-23.5268</v>
+        <v>-1.9869</v>
       </c>
       <c r="N17" t="n">
-        <v>-16.1583</v>
+        <v>-3.8806</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.3684</v>
+        <v>1.8936</v>
       </c>
       <c r="P17" t="n">
-        <v>3.6423</v>
+        <v>1.3657</v>
       </c>
       <c r="Q17" t="n">
-        <v>-35.5108</v>
+        <v>-7.2842</v>
       </c>
       <c r="R17" t="n">
-        <v>39.1531</v>
+        <v>8.65</v>
       </c>
       <c r="S17" t="n">
-        <v>8.2447</v>
+        <v>-0.1476999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>9.7271</v>
+        <v>-1.0679</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.4826</v>
+        <v>0.9202</v>
       </c>
       <c r="V17" t="n">
-        <v>-13.5698</v>
+        <v>-3.1821</v>
       </c>
       <c r="W17" t="n">
-        <v>16.1579</v>
+        <v>4.0573</v>
       </c>
       <c r="X17" t="n">
-        <v>-29.7269</v>
+        <v>-7.2394</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SHACKELFORD</t>
+          <t>J. JACKSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.2279</v>
+        <v>-14.2697</v>
       </c>
       <c r="E18" t="n">
-        <v>-15.251</v>
+        <v>-5.788900000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9767999999999999</v>
+        <v>-8.480599999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-9.9398</v>
+        <v>-16.338</v>
       </c>
       <c r="H18" t="n">
-        <v>-7.5787</v>
+        <v>-15.8641</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.3612</v>
+        <v>-0.4739999999999993</v>
       </c>
       <c r="J18" t="n">
-        <v>-7.952900000000001</v>
+        <v>13.9789</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.6981</v>
+        <v>5.5503</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.254799999999999</v>
+        <v>8.4285</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9869</v>
+        <v>-30.3171</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.8806</v>
+        <v>-21.4144</v>
       </c>
       <c r="O18" t="n">
-        <v>1.8936</v>
+        <v>-8.9023</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3657</v>
+        <v>-0.9104999999999996</v>
       </c>
       <c r="Q18" t="n">
-        <v>-7.2842</v>
+        <v>-48.4856</v>
       </c>
       <c r="R18" t="n">
-        <v>8.65</v>
+        <v>47.5749</v>
       </c>
       <c r="S18" t="n">
-        <v>-4.4716</v>
+        <v>-1.582</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.071</v>
+        <v>-2.2761</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4005000000000001</v>
+        <v>0.6940000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.1821</v>
+        <v>4.5608</v>
       </c>
       <c r="W18" t="n">
-        <v>4.0573</v>
+        <v>30.9936</v>
       </c>
       <c r="X18" t="n">
-        <v>-7.2394</v>
+        <v>-26.4324</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. JACKSON</t>
+          <t>L. FISCHER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>-26.0981</v>
+        <v>-19.6101</v>
       </c>
       <c r="E19" t="n">
-        <v>-14.568</v>
+        <v>-4.4397</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.5298</v>
+        <v>-15.1705</v>
       </c>
       <c r="G19" t="n">
-        <v>-16.338</v>
+        <v>-11.5128</v>
       </c>
       <c r="H19" t="n">
-        <v>-15.8641</v>
+        <v>-12.2248</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4739999999999993</v>
+        <v>0.7124999999999995</v>
       </c>
       <c r="J19" t="n">
-        <v>13.9789</v>
+        <v>12.0142</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5503</v>
+        <v>3.9335</v>
       </c>
       <c r="L19" t="n">
-        <v>8.4285</v>
+        <v>8.080500000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-30.3171</v>
+        <v>-23.5268</v>
       </c>
       <c r="N19" t="n">
-        <v>-21.4144</v>
+        <v>-16.1583</v>
       </c>
       <c r="O19" t="n">
-        <v>-8.9023</v>
+        <v>-7.3684</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9104999999999996</v>
+        <v>3.6423</v>
       </c>
       <c r="Q19" t="n">
-        <v>-48.4856</v>
+        <v>-35.5108</v>
       </c>
       <c r="R19" t="n">
-        <v>47.5749</v>
+        <v>39.1531</v>
       </c>
       <c r="S19" t="n">
-        <v>-13.4101</v>
+        <v>1.8297</v>
       </c>
       <c r="T19" t="n">
-        <v>-11.0549</v>
+        <v>2.8993</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.3552</v>
+        <v>-1.0695</v>
       </c>
       <c r="V19" t="n">
-        <v>4.5608</v>
+        <v>-13.5698</v>
       </c>
       <c r="W19" t="n">
-        <v>30.9936</v>
+        <v>16.1579</v>
       </c>
       <c r="X19" t="n">
-        <v>-26.4324</v>
+        <v>-29.7269</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>-41.4988</v>
+        <v>-25.0536</v>
       </c>
       <c r="E20" t="n">
-        <v>-33.9211</v>
+        <v>-20.6199</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.577999999999999</v>
+        <v>-4.4341</v>
       </c>
       <c r="G20" t="n">
         <v>-27.2453</v>
@@ -2014,13 +2014,13 @@
         <v>56.9082</v>
       </c>
       <c r="S20" t="n">
-        <v>-16.2533</v>
+        <v>0.1923999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-13.5837</v>
+        <v>-0.2827999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.6696</v>
+        <v>0.4751000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-4.601999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>32</v>
       </c>
       <c r="D21" t="n">
-        <v>-46.919</v>
+        <v>-54.7214</v>
       </c>
       <c r="E21" t="n">
-        <v>-44.2457</v>
+        <v>-48.3212</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.672599999999999</v>
+        <v>-6.400099999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-74.18089999999999</v>
@@ -2092,13 +2092,13 @@
         <v>69.88289999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>14.5863</v>
+        <v>6.7838</v>
       </c>
       <c r="T21" t="n">
-        <v>9.168100000000001</v>
+        <v>5.092700000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>5.418</v>
+        <v>1.6911</v>
       </c>
       <c r="V21" t="n">
         <v>-2.802500000000001</v>
@@ -2125,13 +2125,13 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>-133.4014</v>
+        <v>-111.7042</v>
       </c>
       <c r="E22" t="n">
-        <v>-65.80720000000001</v>
+        <v>-56.7454</v>
       </c>
       <c r="F22" t="n">
-        <v>-67.59259999999999</v>
+        <v>-54.9596</v>
       </c>
       <c r="G22" t="n">
         <v>-176.7502</v>
@@ -2161,7 +2161,7 @@
         <v>-151.6352</v>
       </c>
       <c r="P22" t="n">
-        <v>85.36250000000003</v>
+        <v>85.36250000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>-533.797</v>
@@ -2170,13 +2170,13 @@
         <v>619.1587999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>9.880700000000003</v>
+        <v>31.5763</v>
       </c>
       <c r="T22" t="n">
-        <v>23.8404</v>
+        <v>32.90170000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-13.9596</v>
+        <v>-1.3257</v>
       </c>
       <c r="V22" t="n">
         <v>-51.8922</v>
